--- a/tools/xlsform_samples/PHQ9.xlsx
+++ b/tools/xlsform_samples/PHQ9.xlsx
@@ -442,14 +442,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -812,7 +812,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>${include_q9} = 'true'</t>
+          <t>true()</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -834,84 +834,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHQ9_scoring</t>
+          <t>PHQ9_depression</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Computed Scores</t>
+          <t>depression (sum_coded) - Sum of all items (0-27 for PHQ-9, 0-24 for PHQ-8). Severity: 0-4 minimal, 5-9 mild, 10-14 moderate, 15-19 moderately severe, 20-27 severe.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>${phq1} + ${phq2} + ${phq3} + ${phq4} + ${phq5} + ${phq6} + ${phq7} + ${phq8} + ${phq9}</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PHQ9_depression</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>depression (sum_coded) - Sum of all items (0-27 for PHQ-9, 0-24 for PHQ-8). Severity: 0-4 minimal, 5-9 mild, 10-14 moderate, 15-19 moderately severe, 20-27 severe.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>${phq1} + ${phq2} + ${phq3} + ${phq4} + ${phq5} + ${phq6} + ${phq7} + ${phq8} + ${phq9}</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PHQ9_scoring</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/PHQ9.xlsx
+++ b/tools/xlsform_samples/PHQ9.xlsx
@@ -1023,7 +1023,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/PHQ9.xlsx
+++ b/tools/xlsform_samples/PHQ9.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -524,32 +524,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>phq1</t>
+          <t>question_head</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Little interest or pleasure in doing things</t>
+          <t>Over the last 2 weeks, how often have you been bothered by any of the following problems?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -563,12 +555,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>phq2</t>
+          <t>phq1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Feeling down, depressed, or hopeless</t>
+          <t>Little interest or pleasure in doing things</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -597,12 +589,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>phq3</t>
+          <t>phq2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trouble falling or staying asleep, or sleeping too much</t>
+          <t>Feeling down, depressed, or hopeless</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -631,12 +623,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>phq4</t>
+          <t>phq3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Feeling tired or having little energy</t>
+          <t>Trouble falling or staying asleep, or sleeping too much</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -665,12 +657,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>phq5</t>
+          <t>phq4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poor appetite or overeating</t>
+          <t>Feeling tired or having little energy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -699,12 +691,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phq6</t>
+          <t>phq5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Feeling bad about yourself - or that you are a failure or have let yourself or your family down</t>
+          <t>Poor appetite or overeating</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -733,12 +725,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>phq7</t>
+          <t>phq6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Trouble concentrating on things, such as reading the newspaper or watching television</t>
+          <t>Feeling bad about yourself - or that you are a failure or have let yourself or your family down</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -767,12 +759,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phq8</t>
+          <t>phq7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Moving or speaking so slowly that other people could have noticed? Or the opposite - being so fidgety or restless that you have been moving around a lot more than usual</t>
+          <t>Trouble concentrating on things, such as reading the newspaper or watching television</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -801,20 +793,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phq9</t>
+          <t>phq8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thoughts that you would be better off dead or of hurting yourself in some way</t>
+          <t>Moving or speaking so slowly that other people could have noticed? Or the opposite - being so fidgety or restless that you have been moving around a lot more than usual</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>true()</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -834,32 +822,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHQ9_depression</t>
+          <t>phq9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>depression (sum_coded) - Sum of all items (0-27 for PHQ-9, 0-24 for PHQ-8). Severity: 0-4 minimal, 5-9 mild, 10-14 moderate, 15-19 moderately severe, 20-27 severe.</t>
+          <t>Thoughts that you would be better off dead or of hurting yourself in some way</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>${phq1} + ${phq2} + ${phq3} + ${phq4} + ${phq5} + ${phq6} + ${phq7} + ${phq8} + ${phq9}</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PHQ9_depression</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>depression (sum_coded) - Sum of all items (0-27 for PHQ-9, 0-24 for PHQ-8). Severity: 0-4 minimal, 5-9 mild, 10-14 moderate, 15-19 moderately severe, 20-27 severe.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>${phq1} + ${phq2} + ${phq3} + ${phq4} + ${phq5} + ${phq6} + ${phq7} + ${phq8} + ${phq9}</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
